--- a/artfynd/A 17975-2024 artfynd.xlsx
+++ b/artfynd/A 17975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69380074</v>
+        <v>69380065</v>
       </c>
       <c r="B2" t="n">
-        <v>97518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skugglosta</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bromopsis ramosa</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Huds.) Holub</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eskelhem, Tjuls 1:54 905 m SSO, Gtl</t>
+          <t>Eskelhem, Tjuls 1:54 685 m SSO, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694616.7348950393</v>
+        <v>694558</v>
       </c>
       <c r="R2" t="n">
-        <v>6372192.805743552</v>
+        <v>6372409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +752,11 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,11 +765,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrblandskog med lövinslag.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69380065</v>
+        <v>69380064</v>
       </c>
       <c r="B3" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Huds.) Holub</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,14 +821,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eskelhem, Tjuls 1:54 685 m SSO, Gtl</t>
+          <t>Eskelhem, Tjuls 1:44 490 m SSO (Tjuls 1:11), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694558.3619689239</v>
+        <v>694572</v>
       </c>
       <c r="R3" t="n">
-        <v>6372408.808636114</v>
+        <v>6372414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +858,9 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,12 +890,7 @@
         <v>69380066</v>
       </c>
       <c r="B4" t="n">
-        <v>97518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694558.3619689239</v>
+        <v>694558</v>
       </c>
       <c r="R4" t="n">
-        <v>6372408.808636114</v>
+        <v>6372409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,19 +964,9 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,53 +993,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69380072</v>
+        <v>69380074</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>178</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skugglosta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Bromopsis ramosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Huds.) Holub</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Eskelhem, Tjuls 1:54 905 m SSO, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694616.7348950393</v>
+        <v>694617</v>
       </c>
       <c r="R5" t="n">
-        <v>6372192.805743552</v>
+        <v>6372193</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,19 +1070,9 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1101,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69380072</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eskelhem, Tjuls 1:54 905 m SSO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694617</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6372193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Eskelhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog med lövinslag.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17975-2024 artfynd.xlsx
+++ b/artfynd/A 17975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69380065</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69380064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69380066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69380074</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,8 +1228,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69380072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>